--- a/Config/Datas/Tables/d_动画方向_AnimationDirectionConfig.xlsx
+++ b/Config/Datas/Tables/d_动画方向_AnimationDirectionConfig.xlsx
@@ -328,267 +328,279 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="46" customHeight="1">
-      <x:c r="A1" s="11" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B1" s="11" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="C1" s="11" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="D1" s="11" t="str">
-        <x:v>x</x:v>
-      </x:c>
-      <x:c r="E1" s="11" t="str">
-        <x:v>y</x:v>
-      </x:c>
-      <x:c r="F1" s="11" t="str">
-        <x:v>actionIndex</x:v>
-      </x:c>
-      <x:c r="G1" s="11" t="str">
-        <x:v>flipX</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="12" t="str">
-        <x:v>##type</x:v>
-      </x:c>
-      <x:c r="B2" s="12" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C2" s="12" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" s="12" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="E2" s="12" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="F2" s="12" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="G2" s="12" t="str">
-        <x:v>bool</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="32" customHeight="1">
-      <x:c r="A3" s="8" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B3" s="8"/>
-      <x:c r="C3" s="8"/>
-      <x:c r="D3" s="8"/>
-      <x:c r="E3" s="8"/>
-      <x:c r="F3" s="8"/>
-      <x:c r="G3" s="8"/>
-    </x:row>
-    <x:row r="4" ht="70" customHeight="1">
-      <x:c r="A4" s="8" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>方向ID</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
-        <x:v>方向</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="str">
-        <x:v>方向向量X</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="str">
-        <x:v>方向向量Y</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="str">
-        <x:v>旧 FaceActionIndex 映射</x:v>
-      </x:c>
-      <x:c r="G4" s="8" t="str">
-        <x:v>旧 FaceFlipped 映射</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="8"/>
-      <x:c r="B5" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
-        <x:v>右下</x:v>
-      </x:c>
-      <x:c r="D5" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="8" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F5" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="9" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="8"/>
-      <x:c r="B6" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
-        <x:v>下</x:v>
-      </x:c>
-      <x:c r="D6" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E6" s="8" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G6" s="9" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="8"/>
-      <x:c r="B7" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
-        <x:v>左下</x:v>
-      </x:c>
-      <x:c r="D7" s="8" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="E7" s="8" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="9" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="32" customHeight="1">
-      <x:c r="A8" s="8"/>
-      <x:c r="B8" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="str">
-        <x:v>左</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="E8" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="32" customHeight="1">
-      <x:c r="A9" s="8"/>
-      <x:c r="B9" s="8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="8" t="str">
-        <x:v>左上</x:v>
-      </x:c>
-      <x:c r="D9" s="8" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="E9" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G9" s="9" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="32" customHeight="1">
-      <x:c r="A10" s="8"/>
-      <x:c r="B10" s="8" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="8" t="str">
-        <x:v>上</x:v>
-      </x:c>
-      <x:c r="D10" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E10" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F10" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G10" s="9" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="32" customHeight="1">
-      <x:c r="A11" s="8"/>
-      <x:c r="B11" s="8" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="8" t="str">
-        <x:v>右上</x:v>
-      </x:c>
-      <x:c r="D11" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F11" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G11" s="9" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="32" customHeight="1">
-      <x:c r="A12" s="8"/>
-      <x:c r="B12" s="8" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="8" t="str">
-        <x:v>右</x:v>
-      </x:c>
-      <x:c r="D12" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G12" s="9" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="11" t="str">
+        <v>##</v>
+      </c>
+      <c r="B1" s="11" t="str">
+        <v>id</v>
+      </c>
+      <c r="C1" s="11" t="str">
+        <v>name</v>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>xMilli</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>yMilli</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="str">
+        <v>actionIndex</v>
+      </c>
+      <c r="G1" s="11" t="str">
+        <v>flipX</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="12" t="str">
+        <v>##type</v>
+      </c>
+      <c r="B2" s="12" t="str">
+        <v>int</v>
+      </c>
+      <c r="C2" s="12" t="str">
+        <v>string</v>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="str">
+        <v>int</v>
+      </c>
+      <c r="G2" s="12" t="str">
+        <v>bool</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="8" t="str">
+        <v>##var</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="8" t="str">
+        <v>##</v>
+      </c>
+      <c r="B4" s="8" t="str">
+        <v>方向ID</v>
+      </c>
+      <c r="C4" s="8" t="str">
+        <v>方向</v>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>方向向量X；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>方向向量Y；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="str">
+        <v>旧 FaceActionIndex 映射</v>
+      </c>
+      <c r="G4" s="8" t="str">
+        <v>旧 FaceFlipped 映射</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="str">
+        <v>右下</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1000</v>
+      </c>
+      <c r="E5" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="8" t="str">
+        <v>下</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="8" t="str">
+        <v>左下</v>
+      </c>
+      <c r="D7" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="E7" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="8" t="str">
+        <v>左</v>
+      </c>
+      <c r="D8" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="8" t="str">
+        <v>左上</v>
+      </c>
+      <c r="D9" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="8" t="str">
+        <v>上</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="8" t="str">
+        <v>右上</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <v>右</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>